--- a/www/ig/fhir/ror/StructureDefinition-ror-location-supported-capacity.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-location-supported-capacity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="210">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -630,6 +630,27 @@
   </si>
   <si>
     <t>CapacitePriseCharge.affectationTemporaire</t>
+  </si>
+  <si>
+    <t>Extension.extension:comment</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>Extension.extension:comment.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:comment.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:comment.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:comment.value[x]</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
   </si>
   <si>
     <t>base64Binary
@@ -941,7 +962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.68359375" customWidth="true" bestFit="true"/>
@@ -7275,18 +7296,20 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>84</v>
@@ -7301,24 +7324,22 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>76</v>
@@ -7360,33 +7381,33 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7397,7 +7418,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>76</v>
@@ -7409,13 +7430,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7466,24 +7487,558 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AG61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI61" t="s" s="2">
+      <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="AJ64" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AK64" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>111</v>
       </c>
     </row>
